--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92935</v>
+        <v>92938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92938</v>
+        <v>92939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92939</v>
+        <v>92944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136274371</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35507-2022 artfynd.xlsx
+++ b/artfynd/A 35507-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274360</v>
       </c>
       <c r="B2" t="n">
-        <v>92944</v>
+        <v>92946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136274871</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
